--- a/output/laminas_comunales/comunal_o_ocup_a_2024_antofagasta.xlsx
+++ b/output/laminas_comunales/comunal_o_ocup_a_2024_antofagasta.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C85"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -375,16 +375,16 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2102</t>
+          <t>2302</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Mejillones</t>
+          <t>María Elena</t>
         </is>
       </c>
       <c r="C2">
-        <v>48.7426738017467</v>
+        <v>65.0201612903226</v>
       </c>
     </row>
     <row r="3">
@@ -399,22 +399,22 @@
         </is>
       </c>
       <c r="C3">
-        <v>47.5636250775916</v>
+        <v>64.69359331476321</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2302</t>
+          <t>2102</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>María Elena</t>
+          <t>Mejillones</t>
         </is>
       </c>
       <c r="C4">
-        <v>47.5</v>
+        <v>64.1831648413367</v>
       </c>
     </row>
     <row r="5">
@@ -429,7 +429,7 @@
         </is>
       </c>
       <c r="C5">
-        <v>45.3333964611039</v>
+        <v>62.1449797131265</v>
       </c>
     </row>
     <row r="6">
@@ -444,67 +444,1192 @@
         </is>
       </c>
       <c r="C6">
-        <v>44.707062417362</v>
+        <v>61.1309983953524</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2202</t>
+          <t>2101</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Ollagüe</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="C7">
-        <v>40.0914634146341</v>
+        <v>61.1278662279872</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2203</t>
+          <t>2302</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>San Pedro de Atacama</t>
+          <t>María Elena</t>
         </is>
       </c>
       <c r="C8">
-        <v>38.8698974462095</v>
+        <v>61.1263234757211</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2104</t>
+          <t>2101</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Taltal</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="C9">
-        <v>36.099364165317</v>
+        <v>60.9560647413766</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Mejillones</t>
+        </is>
+      </c>
+      <c r="C10">
+        <v>58.8102261553589</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2201</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Calama</t>
+        </is>
+      </c>
+      <c r="C11">
+        <v>57.8674526280584</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2103</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Sierra Gorda</t>
+        </is>
+      </c>
+      <c r="C12">
+        <v>57.7777777777778</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2101</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="C13">
+        <v>57.5232061792804</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2202</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Ollagüe</t>
+        </is>
+      </c>
+      <c r="C14">
+        <v>57.3809523809524</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2101</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="C15">
+        <v>57.2678586313245</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2202</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Ollagüe</t>
+        </is>
+      </c>
+      <c r="C16">
+        <v>57.037037037037</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2101</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="C17">
+        <v>56.8475371362153</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2302</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>María Elena</t>
+        </is>
+      </c>
+      <c r="C18">
+        <v>56.6085179946566</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>2301</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>Tocopilla</t>
         </is>
       </c>
-      <c r="C10">
+      <c r="C19">
+        <v>56.1013359400456</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2104</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Taltal</t>
+        </is>
+      </c>
+      <c r="C20">
+        <v>55.9097057828881</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Mejillones</t>
+        </is>
+      </c>
+      <c r="C21">
+        <v>55.2084588504639</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2103</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Sierra Gorda</t>
+        </is>
+      </c>
+      <c r="C22">
+        <v>55.0317796610169</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2301</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Tocopilla</t>
+        </is>
+      </c>
+      <c r="C23">
+        <v>54.2335191127625</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2201</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Calama</t>
+        </is>
+      </c>
+      <c r="C24">
+        <v>53.2227049023853</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2101</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="C25">
+        <v>52.1587381030856</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2101</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="C26">
+        <v>51.9981437804507</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2101</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="C27">
+        <v>51.8546789642951</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2301</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Tocopilla</t>
+        </is>
+      </c>
+      <c r="C28">
+        <v>50.3304419661297</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2203</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>San Pedro de Atacama</t>
+        </is>
+      </c>
+      <c r="C29">
+        <v>50.2146397592494</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Mejillones</t>
+        </is>
+      </c>
+      <c r="C30">
+        <v>48.7426738017467</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2301</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Tocopilla</t>
+        </is>
+      </c>
+      <c r="C31">
+        <v>48.2492257882883</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2104</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Taltal</t>
+        </is>
+      </c>
+      <c r="C32">
+        <v>47.8566796368353</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2103</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Sierra Gorda</t>
+        </is>
+      </c>
+      <c r="C33">
+        <v>47.5636250775916</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2302</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>María Elena</t>
+        </is>
+      </c>
+      <c r="C34">
+        <v>47.5</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2301</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Tocopilla</t>
+        </is>
+      </c>
+      <c r="C35">
+        <v>46.4656764660613</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2201</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Calama</t>
+        </is>
+      </c>
+      <c r="C36">
+        <v>45.3333964611039</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2101</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="C37">
+        <v>44.707062417362</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2101</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="C38">
+        <v>44.6099524147008</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2301</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Tocopilla</t>
+        </is>
+      </c>
+      <c r="C39">
+        <v>44.4871087403047</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2101</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="C40">
+        <v>44.3663541598374</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2203</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>San Pedro de Atacama</t>
+        </is>
+      </c>
+      <c r="C41">
+        <v>44.1806934254064</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2202</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Ollagüe</t>
+        </is>
+      </c>
+      <c r="C42">
+        <v>44.1468253968254</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2104</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Taltal</t>
+        </is>
+      </c>
+      <c r="C43">
+        <v>42.7645727221279</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2103</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Sierra Gorda</t>
+        </is>
+      </c>
+      <c r="C44">
+        <v>41.7081949058693</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2203</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>San Pedro de Atacama</t>
+        </is>
+      </c>
+      <c r="C45">
+        <v>41.4216653512234</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2202</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Ollagüe</t>
+        </is>
+      </c>
+      <c r="C46">
+        <v>40.0914634146341</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Mejillones</t>
+        </is>
+      </c>
+      <c r="C47">
+        <v>39.9315818281336</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Mejillones</t>
+        </is>
+      </c>
+      <c r="C48">
+        <v>39.4229865614134</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2203</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>San Pedro de Atacama</t>
+        </is>
+      </c>
+      <c r="C49">
+        <v>38.8698974462095</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2301</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Tocopilla</t>
+        </is>
+      </c>
+      <c r="C50">
+        <v>37.7615049144047</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2302</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>María Elena</t>
+        </is>
+      </c>
+      <c r="C51">
+        <v>37.4848799032314</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2201</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Calama</t>
+        </is>
+      </c>
+      <c r="C52">
+        <v>37.3758400608648</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2101</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="C53">
+        <v>37.3148983492475</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2101</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="C54">
+        <v>37.1622626449732</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2103</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Sierra Gorda</t>
+        </is>
+      </c>
+      <c r="C55">
+        <v>37.008281573499</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2101</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="C56">
+        <v>36.8042509509234</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2203</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>San Pedro de Atacama</t>
+        </is>
+      </c>
+      <c r="C57">
+        <v>36.2187371873719</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2104</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Taltal</t>
+        </is>
+      </c>
+      <c r="C58">
+        <v>36.099364165317</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2301</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Tocopilla</t>
+        </is>
+      </c>
+      <c r="C59">
         <v>35.9317250444599</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2202</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Ollagüe</t>
+        </is>
+      </c>
+      <c r="C60">
+        <v>35.8333333333333</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2101</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="C61">
+        <v>35.5332936470881</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2101</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="C62">
+        <v>35.4342206915474</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2101</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="C63">
+        <v>35.002646567127</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2201</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Calama</t>
+        </is>
+      </c>
+      <c r="C64">
+        <v>34.9323428430934</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2302</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>María Elena</t>
+        </is>
+      </c>
+      <c r="C65">
+        <v>34.547305764411</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2203</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>San Pedro de Atacama</t>
+        </is>
+      </c>
+      <c r="C66">
+        <v>33.7231124584957</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2301</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Tocopilla</t>
+        </is>
+      </c>
+      <c r="C67">
+        <v>29.8391633425386</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2301</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Tocopilla</t>
+        </is>
+      </c>
+      <c r="C68">
+        <v>28.9206698447623</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2301</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Tocopilla</t>
+        </is>
+      </c>
+      <c r="C69">
+        <v>28.7929849602199</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2104</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Taltal</t>
+        </is>
+      </c>
+      <c r="C70">
+        <v>28.5844180704441</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2301</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Tocopilla</t>
+        </is>
+      </c>
+      <c r="C71">
+        <v>27.2233664107845</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2104</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Taltal</t>
+        </is>
+      </c>
+      <c r="C72">
+        <v>27.1482277121375</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2202</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Ollagüe</t>
+        </is>
+      </c>
+      <c r="C73">
+        <v>24.1935483870968</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2202</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Ollagüe</t>
+        </is>
+      </c>
+      <c r="C74">
+        <v>24.0384615384615</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2302</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>María Elena</t>
+        </is>
+      </c>
+      <c r="C75">
+        <v>23.3943089430894</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Mejillones</t>
+        </is>
+      </c>
+      <c r="C76">
+        <v>21.6994205089443</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2103</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Sierra Gorda</t>
+        </is>
+      </c>
+      <c r="C77">
+        <v>17.8282828282828</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2201</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Calama</t>
+        </is>
+      </c>
+      <c r="C78">
+        <v>15.3695925257125</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2101</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="C79">
+        <v>15.362326254403</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2101</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="C80">
+        <v>15.2187636296857</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2101</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="C81">
+        <v>15.1763264266845</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2301</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Tocopilla</t>
+        </is>
+      </c>
+      <c r="C82">
+        <v>13.8933590816436</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2104</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Taltal</t>
+        </is>
+      </c>
+      <c r="C83">
+        <v>13.38146811071</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2301</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Tocopilla</t>
+        </is>
+      </c>
+      <c r="C84">
+        <v>12.4490174267705</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2203</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>San Pedro de Atacama</t>
+        </is>
+      </c>
+      <c r="C85">
+        <v>11.4369339518445</v>
       </c>
     </row>
   </sheetData>
